--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92529</v>
+        <v>92603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92603</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92609</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126592988</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,14 +877,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
+        <v>91765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +978,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126592988</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126592988</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126592988</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126592988</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30021-2025 artfynd.xlsx
+++ b/artfynd/A 30021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126592991</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126592990</v>
       </c>
       <c r="B4" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
